--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.07466581131744</v>
+        <v>5.699633194339085</v>
       </c>
       <c r="D2" t="n">
-        <v>35.29741330229972</v>
+        <v>5.735829661623705</v>
       </c>
       <c r="E2" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F2" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.51958347862219</v>
+        <v>7.396932315276106</v>
       </c>
       <c r="D3" t="n">
-        <v>46.48849102869567</v>
+        <v>7.554379792163046</v>
       </c>
       <c r="E3" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F3" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.85565166074898</v>
+        <v>6.476543394871709</v>
       </c>
       <c r="D4" t="n">
-        <v>40.91115190357115</v>
+        <v>6.648062184330311</v>
       </c>
       <c r="E4" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F4" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.21321117771027</v>
+        <v>3.772146816377918</v>
       </c>
       <c r="D5" t="n">
-        <v>24.34871103872164</v>
+        <v>3.956665543792266</v>
       </c>
       <c r="E5" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F5" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.32999216864624</v>
+        <v>5.091123727405015</v>
       </c>
       <c r="D6" t="n">
-        <v>31.65490701589901</v>
+        <v>5.143922390083588</v>
       </c>
       <c r="E6" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F6" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.44650503392294</v>
+        <v>2.347557068012478</v>
       </c>
       <c r="D7" t="n">
-        <v>14.25205206613676</v>
+        <v>2.315958460747224</v>
       </c>
       <c r="E7" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F7" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.11340532343364</v>
+        <v>3.268428365057966</v>
       </c>
       <c r="D8" t="n">
-        <v>20.64895986366405</v>
+        <v>3.355455977845409</v>
       </c>
       <c r="E8" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F8" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.90405305674853</v>
+        <v>3.884408621721637</v>
       </c>
       <c r="D9" t="n">
-        <v>23.8090099154593</v>
+        <v>3.868964111262136</v>
       </c>
       <c r="E9" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F9" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.21937693158491</v>
+        <v>2.798148751382548</v>
       </c>
       <c r="D10" t="n">
-        <v>17.24908960676465</v>
+        <v>2.802977061099256</v>
       </c>
       <c r="E10" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F10" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.58305798949152</v>
+        <v>3.507246923292372</v>
       </c>
       <c r="D11" t="n">
-        <v>20.98938957173228</v>
+        <v>3.410775805406495</v>
       </c>
       <c r="E11" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F11" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.30035188047576</v>
+        <v>2.486307180577312</v>
       </c>
       <c r="D12" t="n">
-        <v>15.63084045256984</v>
+        <v>2.540011573542598</v>
       </c>
       <c r="E12" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F12" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.87256195022463</v>
+        <v>3.391791316911502</v>
       </c>
       <c r="D13" t="n">
-        <v>21.34056252826062</v>
+        <v>3.46784141084235</v>
       </c>
       <c r="E13" t="n">
-        <v>9.575868968021849</v>
+        <v>1.556078707303551</v>
       </c>
       <c r="F13" t="n">
-        <v>9.855616296082912</v>
+        <v>1.601537648113473</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
